--- a/block_effect.xlsx
+++ b/block_effect.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="block_effect" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -1752,10 +1752,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(block_effect!$Q$28,block_effect!$Q$29,block_effect!$Q$30)</c:f>
+              <c:f>(block_effect!$Q$28,block_effect!$Q$29,block_effect!$Q$30,block_effect!$Q$31)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>5190</c:v>
                 </c:pt>
@@ -1764,6 +1764,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>12800</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21900</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
